--- a/DirectX/Bin/Asset/Brotato/tables/Weapon.xlsx
+++ b/DirectX/Bin/Asset/Brotato/tables/Weapon.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jglee\ASTR\AstrDX\DirectX\Bin\Asset\Brotato\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B944EB0-00C9-4FF5-B97E-82845D844C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C1E810-4826-41CF-8B12-1C80CE52EA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{D120B664-9625-4DC7-9A8C-DD4CF0EBB165}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -30,10 +30,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Type</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>BaseDamage</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -144,6 +140,14 @@
   </si>
   <si>
     <t>DamageScale3_Percent</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>bIsMeleeWeapon</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1116,10 +1120,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F041C6E9-5782-4583-B661-038F00A20FAE}">
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1127,281 +1131,296 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
       <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>11</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
+        <v>14</v>
+      </c>
+      <c r="X1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="U1" t="s">
-        <v>14</v>
-      </c>
-      <c r="V1" t="s">
-        <v>15</v>
-      </c>
-      <c r="W1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>128</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>8</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>6</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>100</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>780</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>1</v>
-      </c>
-      <c r="P2">
-        <v>150</v>
       </c>
       <c r="Q2">
         <v>150</v>
       </c>
       <c r="R2">
+        <v>150</v>
+      </c>
+      <c r="S2">
         <v>15</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>0</v>
       </c>
-      <c r="AE2">
+      <c r="AF2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>128</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>16</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>6</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>100</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>730</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>1</v>
-      </c>
-      <c r="P3">
-        <v>150</v>
       </c>
       <c r="Q3">
         <v>150</v>
       </c>
       <c r="R3">
+        <v>150</v>
+      </c>
+      <c r="S3">
         <v>15</v>
       </c>
-      <c r="AE3">
+      <c r="AF3">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>128</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>32</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>6</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>100</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>690</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>1</v>
-      </c>
-      <c r="P4">
-        <v>150</v>
       </c>
       <c r="Q4">
         <v>150</v>
       </c>
       <c r="R4">
+        <v>150</v>
+      </c>
+      <c r="S4">
         <v>15</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>128</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>64</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>100</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>590</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>1</v>
-      </c>
-      <c r="P5">
-        <v>150</v>
       </c>
       <c r="Q5">
         <v>150</v>
       </c>
       <c r="R5">
+        <v>150</v>
+      </c>
+      <c r="S5">
         <v>15</v>
       </c>
-      <c r="AE5">
+      <c r="AF5">
         <v>91</v>
       </c>
     </row>

--- a/DirectX/Bin/Asset/Brotato/tables/Weapon.xlsx
+++ b/DirectX/Bin/Asset/Brotato/tables/Weapon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jglee\ASTR\AstrDX\DirectX\Bin\Asset\Brotato\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C1E810-4826-41CF-8B12-1C80CE52EA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EF37A0-2D27-4312-9705-67F1310FEFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{D120B664-9625-4DC7-9A8C-DD4CF0EBB165}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -148,6 +148,14 @@
   </si>
   <si>
     <t>bIsMeleeWeapon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColliderSizeX</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColliderSizeY</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1120,10 +1128,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F041C6E9-5782-4583-B661-038F00A20FAE}">
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1137,91 +1145,97 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>34</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>32</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>7</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>10</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>11</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>12</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>23</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>13</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>14</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>16</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>18</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>20</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>21</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>22</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1235,46 +1249,52 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>128</v>
+        <v>40</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
+        <v>128</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>8</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>6</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>100</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>780</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>1</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>150</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>150</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>15</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>0</v>
       </c>
-      <c r="AF2">
+      <c r="AH2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1288,43 +1308,49 @@
         <v>29</v>
       </c>
       <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>40</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>128</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>16</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>6</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>100</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>730</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>1</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>150</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>150</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>15</v>
       </c>
-      <c r="AF3">
+      <c r="AH3">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1338,43 +1364,49 @@
         <v>29</v>
       </c>
       <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4">
+        <v>40</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>128</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>32</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>6</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>100</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>690</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>1</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>150</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>150</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>15</v>
       </c>
-      <c r="AF4">
+      <c r="AH4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1388,39 +1420,45 @@
         <v>29</v>
       </c>
       <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>128</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>4</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>64</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>6</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>100</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>590</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>1</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>150</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>150</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>15</v>
       </c>
-      <c r="AF5">
+      <c r="AH5">
         <v>91</v>
       </c>
     </row>
